--- a/data/nzd0117/nzd0117.xlsx
+++ b/data/nzd0117/nzd0117.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E239"/>
+  <dimension ref="A1:E240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5451,6 +5451,27 @@
         <v>326.36</v>
       </c>
       <c r="E239" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>378.01</v>
+      </c>
+      <c r="C240" t="n">
+        <v>323.18</v>
+      </c>
+      <c r="D240" t="n">
+        <v>327.82</v>
+      </c>
+      <c r="E240" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -5467,7 +5488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B290"/>
+  <dimension ref="A1:B291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8370,6 +8391,16 @@
       </c>
       <c r="B290" t="n">
         <v>0.45</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>0.67</v>
       </c>
     </row>
   </sheetData>
@@ -8538,28 +8569,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.242776750437714</v>
+        <v>-0.2422743246209596</v>
       </c>
       <c r="J2" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K2" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01848535573821253</v>
+        <v>0.01857446675952812</v>
       </c>
       <c r="M2" t="n">
-        <v>9.889766576711725</v>
+        <v>9.850472517919339</v>
       </c>
       <c r="N2" t="n">
-        <v>164.213779871923</v>
+        <v>163.5281566719841</v>
       </c>
       <c r="O2" t="n">
-        <v>12.81459245828454</v>
+        <v>12.78781281814776</v>
       </c>
       <c r="P2" t="n">
-        <v>383.7583695511926</v>
+        <v>383.753075170708</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8616,28 +8647,28 @@
         <v>0.0653</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3334346524481255</v>
+        <v>0.3249249952775068</v>
       </c>
       <c r="J3" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K3" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08109546960349967</v>
+        <v>0.0775173526393973</v>
       </c>
       <c r="M3" t="n">
-        <v>6.39576559054318</v>
+        <v>6.395414336748051</v>
       </c>
       <c r="N3" t="n">
-        <v>66.1030811072457</v>
+        <v>66.24639900644139</v>
       </c>
       <c r="O3" t="n">
-        <v>8.130380133010123</v>
+        <v>8.139189087767981</v>
       </c>
       <c r="P3" t="n">
-        <v>324.5483530699622</v>
+        <v>324.6380247415852</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8694,28 +8725,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02201330586938811</v>
+        <v>0.01213192057445972</v>
       </c>
       <c r="J4" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K4" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005652443270283136</v>
+        <v>0.0001711470832312934</v>
       </c>
       <c r="M4" t="n">
-        <v>5.105540326590863</v>
+        <v>5.125297186331468</v>
       </c>
       <c r="N4" t="n">
-        <v>44.95885171472191</v>
+        <v>45.33692290070027</v>
       </c>
       <c r="O4" t="n">
-        <v>6.70513621895349</v>
+        <v>6.733269852062984</v>
       </c>
       <c r="P4" t="n">
-        <v>338.9507043996377</v>
+        <v>339.0548308432278</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -8753,7 +8784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E239"/>
+  <dimension ref="A1:E240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15209,6 +15240,33 @@
         </is>
       </c>
     </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>-36.15193028273257,175.44678647955098</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>-36.15262722920544,175.44746093847886</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>-36.15281214748638,175.44833019162405</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0117/nzd0117.xlsx
+++ b/data/nzd0117/nzd0117.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E240"/>
+  <dimension ref="A1:E241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5472,6 +5472,27 @@
         <v>327.82</v>
       </c>
       <c r="E240" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>384.07</v>
+      </c>
+      <c r="C241" t="n">
+        <v>323.82</v>
+      </c>
+      <c r="D241" t="n">
+        <v>330.68</v>
+      </c>
+      <c r="E241" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -5488,7 +5509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B291"/>
+  <dimension ref="A1:B292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8401,6 +8422,16 @@
       </c>
       <c r="B291" t="n">
         <v>0.67</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
@@ -8569,28 +8600,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2422743246209596</v>
+        <v>-0.2366436122893947</v>
       </c>
       <c r="J2" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K2" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01857446675952812</v>
+        <v>0.01787600637843811</v>
       </c>
       <c r="M2" t="n">
-        <v>9.850472517919339</v>
+        <v>9.832393820274865</v>
       </c>
       <c r="N2" t="n">
-        <v>163.5281566719841</v>
+        <v>163.0302282569224</v>
       </c>
       <c r="O2" t="n">
-        <v>12.78781281814776</v>
+        <v>12.76832910982962</v>
       </c>
       <c r="P2" t="n">
-        <v>383.753075170708</v>
+        <v>383.6933999570249</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8647,28 +8678,28 @@
         <v>0.0653</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3249249952775068</v>
+        <v>0.317046325787461</v>
       </c>
       <c r="J3" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K3" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0775173526393973</v>
+        <v>0.07433212434462588</v>
       </c>
       <c r="M3" t="n">
-        <v>6.395414336748051</v>
+        <v>6.392734428672431</v>
       </c>
       <c r="N3" t="n">
-        <v>66.24639900644139</v>
+        <v>66.32951792892835</v>
       </c>
       <c r="O3" t="n">
-        <v>8.139189087767981</v>
+        <v>8.144293580718241</v>
       </c>
       <c r="P3" t="n">
-        <v>324.6380247415852</v>
+        <v>324.7215241742807</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8725,28 +8756,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01213192057445972</v>
+        <v>0.004800578960542807</v>
       </c>
       <c r="J4" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K4" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001711470832312934</v>
+        <v>2.686200646750958e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>5.125297186331468</v>
+        <v>5.134794587906025</v>
       </c>
       <c r="N4" t="n">
-        <v>45.33692290070027</v>
+        <v>45.45899849775372</v>
       </c>
       <c r="O4" t="n">
-        <v>6.733269852062984</v>
+        <v>6.742328863067547</v>
       </c>
       <c r="P4" t="n">
-        <v>339.0548308432278</v>
+        <v>339.1325296052374</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -8784,7 +8815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E240"/>
+  <dimension ref="A1:E241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15267,6 +15298,33 @@
         </is>
       </c>
     </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>-36.151878107061805,175.44680632902467</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>-36.15262171889885,175.44746303478294</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>-36.15278752326939,175.44833955931776</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0117/nzd0117.xlsx
+++ b/data/nzd0117/nzd0117.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E241"/>
+  <dimension ref="A1:E242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5493,6 +5493,27 @@
         <v>330.68</v>
       </c>
       <c r="E241" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>389.44</v>
+      </c>
+      <c r="C242" t="n">
+        <v>326.21</v>
+      </c>
+      <c r="D242" t="n">
+        <v>334.33</v>
+      </c>
+      <c r="E242" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -5509,7 +5530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B292"/>
+  <dimension ref="A1:B293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8432,6 +8453,16 @@
       </c>
       <c r="B292" t="n">
         <v>0.49</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>-0.45</v>
       </c>
     </row>
   </sheetData>
@@ -8600,28 +8631,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2366436122893947</v>
+        <v>-0.2265012522805959</v>
       </c>
       <c r="J2" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K2" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01787600637843811</v>
+        <v>0.0164922092655454</v>
       </c>
       <c r="M2" t="n">
-        <v>9.832393820274865</v>
+        <v>9.832544961879735</v>
       </c>
       <c r="N2" t="n">
-        <v>163.0302282569224</v>
+        <v>162.9430759745549</v>
       </c>
       <c r="O2" t="n">
-        <v>12.76832910982962</v>
+        <v>12.76491582324595</v>
       </c>
       <c r="P2" t="n">
-        <v>383.6933999570249</v>
+        <v>383.5851033819146</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8678,28 +8709,28 @@
         <v>0.0653</v>
       </c>
       <c r="I3" t="n">
-        <v>0.317046325787461</v>
+        <v>0.3112174134880078</v>
       </c>
       <c r="J3" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K3" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07433212434462588</v>
+        <v>0.07224038306942249</v>
       </c>
       <c r="M3" t="n">
-        <v>6.392734428672431</v>
+        <v>6.383511473635403</v>
       </c>
       <c r="N3" t="n">
-        <v>66.32951792892835</v>
+        <v>66.24893948075406</v>
       </c>
       <c r="O3" t="n">
-        <v>8.144293580718241</v>
+        <v>8.139345150609726</v>
       </c>
       <c r="P3" t="n">
-        <v>324.7215241742807</v>
+        <v>324.783763262432</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8756,28 +8787,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004800578960542807</v>
+        <v>0.0006334238353863284</v>
       </c>
       <c r="J4" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K4" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L4" t="n">
-        <v>2.686200646750958e-05</v>
+        <v>4.709956819004546e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>5.134794587906025</v>
+        <v>5.131025145814193</v>
       </c>
       <c r="N4" t="n">
-        <v>45.45899849775372</v>
+        <v>45.36985605812546</v>
       </c>
       <c r="O4" t="n">
-        <v>6.742328863067547</v>
+        <v>6.735714962654333</v>
       </c>
       <c r="P4" t="n">
-        <v>339.1325296052374</v>
+        <v>339.1770250311162</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -8815,7 +8846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E241"/>
+  <dimension ref="A1:E242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15325,6 +15356,33 @@
         </is>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>-36.151831872182974,175.44682391838927</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>-36.15260114134741,175.44747086316616</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>-36.15275609725731,175.4483515145833</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0117/nzd0117.xlsx
+++ b/data/nzd0117/nzd0117.xlsx
@@ -5530,7 +5530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B293"/>
+  <dimension ref="A1:B295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8463,6 +8463,26 @@
       </c>
       <c r="B293" t="n">
         <v>-0.45</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0117/nzd0117.xlsx
+++ b/data/nzd0117/nzd0117.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E242"/>
+  <dimension ref="A1:E245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5516,6 +5516,69 @@
       <c r="E242" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>396.19</v>
+      </c>
+      <c r="C243" t="n">
+        <v>319.94</v>
+      </c>
+      <c r="D243" t="n">
+        <v>339.99</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>392.72</v>
+      </c>
+      <c r="C244" t="n">
+        <v>317.16</v>
+      </c>
+      <c r="D244" t="n">
+        <v>338.08</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>385.95</v>
+      </c>
+      <c r="C245" t="n">
+        <v>315.63</v>
+      </c>
+      <c r="D245" t="n">
+        <v>332.51</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B295"/>
+  <dimension ref="A1:B297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8483,6 +8546,26 @@
       </c>
       <c r="B295" t="n">
         <v>0.26</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>-0.7</v>
       </c>
     </row>
   </sheetData>
@@ -8651,28 +8734,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2265012522805959</v>
+        <v>-0.1915589610021073</v>
       </c>
       <c r="J2" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="K2" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0164922092655454</v>
+        <v>0.01199504276871122</v>
       </c>
       <c r="M2" t="n">
-        <v>9.832544961879735</v>
+        <v>9.856477888859553</v>
       </c>
       <c r="N2" t="n">
-        <v>162.9430759745549</v>
+        <v>163.4993688904085</v>
       </c>
       <c r="O2" t="n">
-        <v>12.76491582324595</v>
+        <v>12.7866871741827</v>
       </c>
       <c r="P2" t="n">
-        <v>383.5851033819146</v>
+        <v>383.2087399017633</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8729,28 +8812,28 @@
         <v>0.0653</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3112174134880078</v>
+        <v>0.2726458670786591</v>
       </c>
       <c r="J3" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="K3" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07224038306942249</v>
+        <v>0.05559217618833301</v>
       </c>
       <c r="M3" t="n">
-        <v>6.383511473635403</v>
+        <v>6.41939344811637</v>
       </c>
       <c r="N3" t="n">
-        <v>66.24893948075406</v>
+        <v>68.31208657430011</v>
       </c>
       <c r="O3" t="n">
-        <v>8.139345150609726</v>
+        <v>8.265112617157742</v>
       </c>
       <c r="P3" t="n">
-        <v>324.783763262432</v>
+        <v>325.1995954267392</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8807,28 +8890,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006334238353863284</v>
+        <v>-0.005201390877403432</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="L4" t="n">
-        <v>4.709956819004546e-07</v>
+        <v>3.252126343866735e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>5.131025145814193</v>
+        <v>5.098991135302352</v>
       </c>
       <c r="N4" t="n">
-        <v>45.36985605812546</v>
+        <v>44.99987029512145</v>
       </c>
       <c r="O4" t="n">
-        <v>6.735714962654333</v>
+        <v>6.708194264861554</v>
       </c>
       <c r="P4" t="n">
-        <v>339.1770250311162</v>
+        <v>339.2400862977659</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -8866,7 +8949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E242"/>
+  <dimension ref="A1:E245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15403,6 +15486,87 @@
         </is>
       </c>
     </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>-36.15177375571218,175.44684602789852</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>-36.1526551251321,175.44745032593514</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>-36.152707365411985,175.44837005341577</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>-36.15180363188351,175.44683466197685</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>-36.15267906052536,175.44744122010502</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>-36.15272381025757,175.44836379738106</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>-36.151861920549536,175.4468124869422</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>-36.15269223360125,175.4474362086208</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>-36.15277176721414,175.4483455533287</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
